--- a/results/count/542_WT__2_z18c1-2/measurements.xlsx
+++ b/results/count/542_WT__2_z18c1-2/measurements.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,189 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v2-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3380.9167</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3413</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1553.2119</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>major_axis_length</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>122.9919</v>
+      </c>
+      <c r="C7" t="n">
+        <v>126.1987</v>
+      </c>
+      <c r="D7" t="n">
+        <v>36.6366</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>minor_axis_length</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>35.2191</v>
+      </c>
+      <c r="C8" t="n">
+        <v>35.1867</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8.7157</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aspect_ratio</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.464</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.4157</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5351</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>eccentricity</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9545</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9560999999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>solidity</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8622</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8944</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>12</v>
       </c>
     </row>

--- a/results/count/542_WT__2_z18c1-2/measurements.xlsx
+++ b/results/count/542_WT__2_z18c1-2/measurements.xlsx
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3380.9167</v>
+        <v>3688.2727</v>
       </c>
       <c r="C6" t="n">
-        <v>3413</v>
+        <v>3684</v>
       </c>
       <c r="D6" t="n">
-        <v>1553.2119</v>
+        <v>1441.7471</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>122.9919</v>
+        <v>132.2753</v>
       </c>
       <c r="C7" t="n">
-        <v>126.1987</v>
+        <v>128.431</v>
       </c>
       <c r="D7" t="n">
-        <v>36.6366</v>
+        <v>35.9804</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35.2191</v>
+        <v>35.8241</v>
       </c>
       <c r="C8" t="n">
-        <v>35.1867</v>
+        <v>35.4482</v>
       </c>
       <c r="D8" t="n">
-        <v>8.7157</v>
+        <v>8.8535</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.464</v>
+        <v>3.6839</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4157</v>
+        <v>3.6773</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5351</v>
+        <v>0.6253</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9545</v>
+        <v>0.9593</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9623</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0136</v>
+        <v>0.0137</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8622</v>
+        <v>0.8643</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8944</v>
+        <v>0.893</v>
       </c>
       <c r="D11" t="n">
-        <v>0.077</v>
+        <v>0.0736</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1039,31 +1039,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1659</v>
+        <v>3684</v>
       </c>
       <c r="C10" t="n">
-        <v>86.319</v>
+        <v>159.3366</v>
       </c>
       <c r="D10" t="n">
-        <v>28.2024</v>
+        <v>32.9692</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0607</v>
+        <v>4.8329</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9784</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8972</v>
+        <v>0.8054</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0131</v>
+        <v>-0.098</v>
       </c>
       <c r="I10" t="n">
-        <v>703.2459</v>
+        <v>739.4517</v>
       </c>
       <c r="J10" t="n">
-        <v>250.5907</v>
+        <v>247.5361</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1079,31 +1079,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2025</v>
+        <v>3421</v>
       </c>
       <c r="C11" t="n">
-        <v>93.8917</v>
+        <v>128.431</v>
       </c>
       <c r="D11" t="n">
-        <v>33.3304</v>
+        <v>34.9252</v>
       </c>
       <c r="E11" t="n">
-        <v>2.817</v>
+        <v>3.6773</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9349</v>
+        <v>0.9623</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7481</v>
+        <v>0.8774</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2341</v>
+        <v>-0.2145</v>
       </c>
       <c r="I11" t="n">
-        <v>769.1136</v>
+        <v>813.822</v>
       </c>
       <c r="J11" t="n">
-        <v>245.0336</v>
+        <v>732.5244</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1119,31 +1119,31 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3421</v>
+        <v>2890</v>
       </c>
       <c r="C12" t="n">
-        <v>128.431</v>
+        <v>110.8033</v>
       </c>
       <c r="D12" t="n">
-        <v>34.9252</v>
+        <v>33.408</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6773</v>
+        <v>3.3167</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9623</v>
+        <v>0.9535</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8774</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2145</v>
+        <v>0.0034</v>
       </c>
       <c r="I12" t="n">
-        <v>813.822</v>
+        <v>944.8156</v>
       </c>
       <c r="J12" t="n">
-        <v>732.5244</v>
+        <v>407.9035</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -1159,76 +1159,36 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2890</v>
+        <v>508</v>
       </c>
       <c r="C13" t="n">
-        <v>110.8033</v>
+        <v>44.3947</v>
       </c>
       <c r="D13" t="n">
-        <v>33.408</v>
+        <v>15.6697</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3167</v>
+        <v>2.8331</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9535</v>
+        <v>0.9356</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.917</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0034</v>
+        <v>-0.2083</v>
       </c>
       <c r="I13" t="n">
-        <v>944.8156</v>
+        <v>990.1555</v>
       </c>
       <c r="J13" t="n">
-        <v>407.9035</v>
+        <v>937.6988</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>508</v>
-      </c>
-      <c r="C14" t="n">
-        <v>44.3947</v>
-      </c>
-      <c r="D14" t="n">
-        <v>15.6697</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2.8331</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.9356</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.2083</v>
-      </c>
-      <c r="I14" t="n">
-        <v>990.1555</v>
-      </c>
-      <c r="J14" t="n">
-        <v>937.6988</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr">
         <is>
           <t>px</t>
         </is>
